--- a/Analysis/clean data/Survey 2_scored_near complete_16.6.26.xlsx
+++ b/Analysis/clean data/Survey 2_scored_near complete_16.6.26.xlsx
@@ -7182,12 +7182,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Multi-country: Australia &amp;New Zealand</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Australia &amp; New Zealand</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
